--- a/CPDS-AD_dataset/scenario_records/FDI_attacks/local_model_consistent/test_data_LMC_4/data_three_phase_meter_5.xlsx
+++ b/CPDS-AD_dataset/scenario_records/FDI_attacks/local_model_consistent/test_data_LMC_4/data_three_phase_meter_5.xlsx
@@ -521,7 +521,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:02.877</t>
+          <t>2026/6/30 00:00:02.877</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -579,7 +579,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:07.532</t>
+          <t>2026/6/30 00:00:07.532</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -637,7 +637,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:12.229</t>
+          <t>2026/6/30 00:00:12.229</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -695,7 +695,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:17.824</t>
+          <t>2026/6/30 00:00:17.824</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -753,7 +753,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:22.466</t>
+          <t>2026/6/30 00:00:22.466</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:27.154</t>
+          <t>2026/6/30 00:00:27.154</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:31.808</t>
+          <t>2026/6/30 00:00:31.808</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -927,7 +927,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:36.799</t>
+          <t>2026/6/30 00:00:36.799</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -985,7 +985,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:41.761</t>
+          <t>2026/6/30 00:00:41.761</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:46.417</t>
+          <t>2026/6/30 00:00:46.417</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:51.106</t>
+          <t>2026/6/30 00:00:51.106</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:56.962</t>
+          <t>2026/6/30 00:00:56.962</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:01.657</t>
+          <t>2026/6/30 00:01:01.657</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:06.300</t>
+          <t>2026/6/30 00:01:06.300</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:10.940</t>
+          <t>2026/6/30 00:01:10.940</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:16.257</t>
+          <t>2026/6/30 00:01:16.257</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:21.225</t>
+          <t>2026/6/30 00:01:21.225</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:25.885</t>
+          <t>2026/6/30 00:01:25.885</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:30.564</t>
+          <t>2026/6/30 00:01:30.564</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:35.547</t>
+          <t>2026/6/30 00:01:35.547</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:40.821</t>
+          <t>2026/6/30 00:01:40.821</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:45.469</t>
+          <t>2026/6/30 00:01:45.469</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:50.155</t>
+          <t>2026/6/30 00:01:50.155</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:55.715</t>
+          <t>2026/6/30 00:01:55.715</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:00.712</t>
+          <t>2026/6/30 00:02:00.712</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:05.358</t>
+          <t>2026/6/30 00:02:05.358</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:10.058</t>
+          <t>2026/6/30 00:02:10.058</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:14.990</t>
+          <t>2026/6/30 00:02:14.990</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:20.300</t>
+          <t>2026/6/30 00:02:20.300</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:24.936</t>
+          <t>2026/6/30 00:02:24.936</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:29.621</t>
+          <t>2026/6/30 00:02:29.621</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:34.564</t>
+          <t>2026/6/30 00:02:34.564</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:39.869</t>
+          <t>2026/6/30 00:02:39.869</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:44.566</t>
+          <t>2026/6/30 00:02:44.566</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:49.183</t>
+          <t>2026/6/30 00:02:49.183</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:54.170</t>
+          <t>2026/6/30 00:02:54.170</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:59.767</t>
+          <t>2026/6/30 00:02:59.767</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:04.433</t>
+          <t>2026/6/30 00:03:04.433</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:09.107</t>
+          <t>2026/6/30 00:03:09.107</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:14.085</t>
+          <t>2026/6/30 00:03:14.085</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:19.026</t>
+          <t>2026/6/30 00:03:19.026</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:23.683</t>
+          <t>2026/6/30 00:03:23.683</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:33.028</t>
+          <t>2026/6/30 00:03:33.028</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:33.028</t>
+          <t>2026/6/30 00:03:33.028</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:38.649</t>
+          <t>2026/6/30 00:03:38.649</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:47.930</t>
+          <t>2026/6/30 00:03:47.930</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:52.600</t>
+          <t>2026/6/30 00:03:52.600</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:58.534</t>
+          <t>2026/6/30 00:03:58.534</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:58.534</t>
+          <t>2026/6/30 00:03:58.534</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:07.842</t>
+          <t>2026/6/30 00:04:07.842</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:12.526</t>
+          <t>2026/6/30 00:04:12.526</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:17.144</t>
+          <t>2026/6/30 00:04:17.144</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:22.160</t>
+          <t>2026/6/30 00:04:22.160</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:26.789</t>
+          <t>2026/6/30 00:04:26.789</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:31.468</t>
+          <t>2026/6/30 00:04:31.468</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:36.781</t>
+          <t>2026/6/30 00:04:36.781</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:41.700</t>
+          <t>2026/6/30 00:04:41.700</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:46.392</t>
+          <t>2026/6/30 00:04:46.392</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:51.030</t>
+          <t>2026/6/30 00:04:51.030</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:56.946</t>
+          <t>2026/6/30 00:04:56.946</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:01.626</t>
+          <t>2026/6/30 00:05:01.626</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:06.897</t>
+          <t>2026/6/30 00:05:06.897</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:11.573</t>
+          <t>2026/6/30 00:05:11.573</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:16.865</t>
+          <t>2026/6/30 00:05:16.865</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:21.821</t>
+          <t>2026/6/30 00:05:21.821</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:26.487</t>
+          <t>2026/6/30 00:05:26.487</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:31.172</t>
+          <t>2026/6/30 00:05:31.172</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:36.436</t>
+          <t>2026/6/30 00:05:36.436</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:41.402</t>
+          <t>2026/6/30 00:05:41.402</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:46.068</t>
+          <t>2026/6/30 00:05:46.068</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:50.732</t>
+          <t>2026/6/30 00:05:50.732</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:56.352</t>
+          <t>2026/6/30 00:05:56.352</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:01.308</t>
+          <t>2026/6/30 00:06:01.308</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:05.963</t>
+          <t>2026/6/30 00:06:05.963</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:10.616</t>
+          <t>2026/6/30 00:06:10.616</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:15.928</t>
+          <t>2026/6/30 00:06:15.928</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:20.913</t>
+          <t>2026/6/30 00:06:20.913</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:25.553</t>
+          <t>2026/6/30 00:06:25.553</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:30.224</t>
+          <t>2026/6/30 00:06:30.224</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:35.172</t>
+          <t>2026/6/30 00:06:35.172</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:40.503</t>
+          <t>2026/6/30 00:06:40.503</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:45.161</t>
+          <t>2026/6/30 00:06:45.161</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:49.824</t>
+          <t>2026/6/30 00:06:49.824</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:55.120</t>
+          <t>2026/6/30 00:06:55.120</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:00.403</t>
+          <t>2026/6/30 00:07:00.403</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:05.359</t>
+          <t>2026/6/30 00:07:05.359</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:10.028</t>
+          <t>2026/6/30 00:07:10.028</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:14.974</t>
+          <t>2026/6/30 00:07:14.974</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:20.263</t>
+          <t>2026/6/30 00:07:20.263</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:24.914</t>
+          <t>2026/6/30 00:07:24.914</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:29.600</t>
+          <t>2026/6/30 00:07:29.600</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:34.576</t>
+          <t>2026/6/30 00:07:34.576</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:39.872</t>
+          <t>2026/6/30 00:07:39.872</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:44.546</t>
+          <t>2026/6/30 00:07:44.546</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:49.162</t>
+          <t>2026/6/30 00:07:49.162</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:53.862</t>
+          <t>2026/6/30 00:07:53.862</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:58.496</t>
+          <t>2026/6/30 00:07:58.496</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:07.808</t>
+          <t>2026/6/30 00:08:07.808</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:12.499</t>
+          <t>2026/6/30 00:08:12.499</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:18.071</t>
+          <t>2026/6/30 00:08:18.071</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:22.775</t>
+          <t>2026/6/30 00:08:22.775</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:27.421</t>
+          <t>2026/6/30 00:08:27.421</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:32.092</t>
+          <t>2026/6/30 00:08:32.092</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:37.390</t>
+          <t>2026/6/30 00:08:37.390</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:42.335</t>
+          <t>2026/6/30 00:08:42.335</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:47.043</t>
+          <t>2026/6/30 00:08:47.043</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:51.680</t>
+          <t>2026/6/30 00:08:51.680</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:57.575</t>
+          <t>2026/6/30 00:08:57.575</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -6785,7 +6785,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:02.219</t>
+          <t>2026/6/30 00:09:02.219</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:06.878</t>
+          <t>2026/6/30 00:09:06.878</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:11.573</t>
+          <t>2026/6/30 00:09:11.573</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:16.867</t>
+          <t>2026/6/30 00:09:16.867</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:21.835</t>
+          <t>2026/6/30 00:09:21.835</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:26.485</t>
+          <t>2026/6/30 00:09:26.485</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:31.147</t>
+          <t>2026/6/30 00:09:31.147</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:36.446</t>
+          <t>2026/6/30 00:09:36.446</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -7249,7 +7249,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:41.410</t>
+          <t>2026/6/30 00:09:41.410</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:46.056</t>
+          <t>2026/6/30 00:09:46.056</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:50.735</t>
+          <t>2026/6/30 00:09:50.735</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:56.339</t>
+          <t>2026/6/30 00:09:56.339</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:01.331</t>
+          <t>2026/6/30 00:10:01.331</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:05.967</t>
+          <t>2026/6/30 00:10:05.967</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:10.647</t>
+          <t>2026/6/30 00:10:10.647</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:15.913</t>
+          <t>2026/6/30 00:10:15.913</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:20.895</t>
+          <t>2026/6/30 00:10:20.895</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:25.560</t>
+          <t>2026/6/30 00:10:25.560</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:30.246</t>
+          <t>2026/6/30 00:10:30.246</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:35.198</t>
+          <t>2026/6/30 00:10:35.198</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -7945,7 +7945,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:40.458</t>
+          <t>2026/6/30 00:10:40.458</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:45.161</t>
+          <t>2026/6/30 00:10:45.161</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:49.775</t>
+          <t>2026/6/30 00:10:49.775</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:55.105</t>
+          <t>2026/6/30 00:10:55.105</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -8177,7 +8177,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:00.340</t>
+          <t>2026/6/30 00:11:00.340</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:05.012</t>
+          <t>2026/6/30 00:11:05.012</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:09.666</t>
+          <t>2026/6/30 00:11:09.666</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:14.657</t>
+          <t>2026/6/30 00:11:14.657</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:19.951</t>
+          <t>2026/6/30 00:11:19.951</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -8467,7 +8467,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:24.591</t>
+          <t>2026/6/30 00:11:24.591</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:29.259</t>
+          <t>2026/6/30 00:11:29.259</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:34.281</t>
+          <t>2026/6/30 00:11:34.281</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:38.935</t>
+          <t>2026/6/30 00:11:38.935</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -8699,7 +8699,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:43.577</t>
+          <t>2026/6/30 00:11:43.577</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:52.893</t>
+          <t>2026/6/30 00:11:52.893</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:58.817</t>
+          <t>2026/6/30 00:11:58.817</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -8873,7 +8873,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:58.817</t>
+          <t>2026/6/30 00:11:58.817</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:08.108</t>
+          <t>2026/6/30 00:12:08.108</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:12.777</t>
+          <t>2026/6/30 00:12:12.777</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -9047,7 +9047,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:18.389</t>
+          <t>2026/6/30 00:12:18.389</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -9105,7 +9105,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:23.045</t>
+          <t>2026/6/30 00:12:23.045</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -9163,7 +9163,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:27.733</t>
+          <t>2026/6/30 00:12:27.733</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:32.361</t>
+          <t>2026/6/30 00:12:32.361</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:37.654</t>
+          <t>2026/6/30 00:12:37.654</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:42.328</t>
+          <t>2026/6/30 00:12:42.328</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:46.989</t>
+          <t>2026/6/30 00:12:46.989</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:51.631</t>
+          <t>2026/6/30 00:12:51.631</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:57.554</t>
+          <t>2026/6/30 00:12:57.554</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -9569,7 +9569,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:02.233</t>
+          <t>2026/6/30 00:13:02.233</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:06.908</t>
+          <t>2026/6/30 00:13:06.908</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:11.544</t>
+          <t>2026/6/30 00:13:11.544</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -9743,7 +9743,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:16.824</t>
+          <t>2026/6/30 00:13:16.824</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:21.795</t>
+          <t>2026/6/30 00:13:21.795</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:26.464</t>
+          <t>2026/6/30 00:13:26.464</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -9917,7 +9917,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:31.153</t>
+          <t>2026/6/30 00:13:31.153</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -9975,7 +9975,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:36.439</t>
+          <t>2026/6/30 00:13:36.439</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:41.386</t>
+          <t>2026/6/30 00:13:41.386</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:46.070</t>
+          <t>2026/6/30 00:13:46.070</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:50.726</t>
+          <t>2026/6/30 00:13:50.726</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:56.327</t>
+          <t>2026/6/30 00:13:56.327</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -10265,7 +10265,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:01.274</t>
+          <t>2026/6/30 00:14:01.274</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:05.962</t>
+          <t>2026/6/30 00:14:05.962</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:10.591</t>
+          <t>2026/6/30 00:14:10.591</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -10439,7 +10439,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:15.928</t>
+          <t>2026/6/30 00:14:15.928</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -10497,7 +10497,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:20.883</t>
+          <t>2026/6/30 00:14:20.883</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:25.551</t>
+          <t>2026/6/30 00:14:25.551</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -10613,7 +10613,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:30.222</t>
+          <t>2026/6/30 00:14:30.222</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -10671,7 +10671,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:35.142</t>
+          <t>2026/6/30 00:14:35.142</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -10729,7 +10729,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:40.469</t>
+          <t>2026/6/30 00:14:40.469</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:45.140</t>
+          <t>2026/6/30 00:14:45.140</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:49.781</t>
+          <t>2026/6/30 00:14:49.781</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:55.079</t>
+          <t>2026/6/30 00:14:55.079</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -10961,7 +10961,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:00.363</t>
+          <t>2026/6/30 00:15:00.363</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -11019,7 +11019,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:05.029</t>
+          <t>2026/6/30 00:15:05.029</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:09.696</t>
+          <t>2026/6/30 00:15:09.696</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:14.657</t>
+          <t>2026/6/30 00:15:14.657</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:19.639</t>
+          <t>2026/6/30 00:15:19.639</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:24.297</t>
+          <t>2026/6/30 00:15:24.297</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:28.969</t>
+          <t>2026/6/30 00:15:28.969</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -11367,7 +11367,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:33.599</t>
+          <t>2026/6/30 00:15:33.599</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -11425,7 +11425,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:39.206</t>
+          <t>2026/6/30 00:15:39.206</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -11483,7 +11483,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:43.864</t>
+          <t>2026/6/30 00:15:43.864</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -11541,7 +11541,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:53.212</t>
+          <t>2026/6/30 00:15:53.212</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:53.212</t>
+          <t>2026/6/30 00:15:53.212</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -11657,7 +11657,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:59.093</t>
+          <t>2026/6/30 00:15:59.093</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:03.764</t>
+          <t>2026/6/30 00:16:03.764</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:13.107</t>
+          <t>2026/6/30 00:16:13.107</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:18.049</t>
+          <t>2026/6/30 00:16:18.049</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -11889,7 +11889,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:22.708</t>
+          <t>2026/6/30 00:16:22.708</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -11947,7 +11947,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:27.388</t>
+          <t>2026/6/30 00:16:27.388</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:32.063</t>
+          <t>2026/6/30 00:16:32.063</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -12063,7 +12063,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:37.362</t>
+          <t>2026/6/30 00:16:37.362</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -12121,7 +12121,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:42.303</t>
+          <t>2026/6/30 00:16:42.303</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:46.974</t>
+          <t>2026/6/30 00:16:46.974</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:51.646</t>
+          <t>2026/6/30 00:16:51.646</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -12295,7 +12295,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:57.560</t>
+          <t>2026/6/30 00:16:57.560</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:02.191</t>
+          <t>2026/6/30 00:17:02.191</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -12411,7 +12411,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:06.878</t>
+          <t>2026/6/30 00:17:06.878</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -12469,7 +12469,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:11.541</t>
+          <t>2026/6/30 00:17:11.541</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -12527,7 +12527,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:16.837</t>
+          <t>2026/6/30 00:17:16.837</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:21.812</t>
+          <t>2026/6/30 00:17:21.812</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -12643,7 +12643,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:26.438</t>
+          <t>2026/6/30 00:17:26.438</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -12701,7 +12701,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:31.108</t>
+          <t>2026/6/30 00:17:31.108</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:36.383</t>
+          <t>2026/6/30 00:17:36.383</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:41.385</t>
+          <t>2026/6/30 00:17:41.385</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -12875,7 +12875,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:46.043</t>
+          <t>2026/6/30 00:17:46.043</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -12933,7 +12933,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:50.709</t>
+          <t>2026/6/30 00:17:50.709</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:56.299</t>
+          <t>2026/6/30 00:17:56.299</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:01.259</t>
+          <t>2026/6/30 00:18:01.259</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -13107,7 +13107,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:05.937</t>
+          <t>2026/6/30 00:18:05.937</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -13165,7 +13165,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:10.584</t>
+          <t>2026/6/30 00:18:10.584</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:15.557</t>
+          <t>2026/6/30 00:18:15.557</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:20.850</t>
+          <t>2026/6/30 00:18:20.850</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -13339,7 +13339,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:25.495</t>
+          <t>2026/6/30 00:18:25.495</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -13397,7 +13397,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:30.197</t>
+          <t>2026/6/30 00:18:30.197</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -13455,7 +13455,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:35.164</t>
+          <t>2026/6/30 00:18:35.164</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:40.433</t>
+          <t>2026/6/30 00:18:40.433</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -13571,7 +13571,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:45.115</t>
+          <t>2026/6/30 00:18:45.115</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -13629,7 +13629,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:49.736</t>
+          <t>2026/6/30 00:18:49.736</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -13687,7 +13687,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:55.012</t>
+          <t>2026/6/30 00:18:55.012</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -13745,7 +13745,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:00.320</t>
+          <t>2026/6/30 00:19:00.320</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -13803,7 +13803,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:04.968</t>
+          <t>2026/6/30 00:19:04.968</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -13861,7 +13861,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:09.619</t>
+          <t>2026/6/30 00:19:09.619</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -13919,7 +13919,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:14.604</t>
+          <t>2026/6/30 00:19:14.604</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -13977,7 +13977,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:19.923</t>
+          <t>2026/6/30 00:19:19.923</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -14035,7 +14035,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:24.592</t>
+          <t>2026/6/30 00:19:24.592</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -14093,7 +14093,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:29.225</t>
+          <t>2026/6/30 00:19:29.225</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:34.187</t>
+          <t>2026/6/30 00:19:34.187</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -14209,7 +14209,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:39.502</t>
+          <t>2026/6/30 00:19:39.502</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -14267,7 +14267,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:44.174</t>
+          <t>2026/6/30 00:19:44.174</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -14325,7 +14325,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:48.810</t>
+          <t>2026/6/30 00:19:48.810</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -14383,7 +14383,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:58.438</t>
+          <t>2026/6/30 00:19:58.438</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:03.401</t>
+          <t>2026/6/30 00:20:03.401</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -14499,7 +14499,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:08.101</t>
+          <t>2026/6/30 00:20:08.101</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -14557,7 +14557,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:12.754</t>
+          <t>2026/6/30 00:20:12.754</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -14615,7 +14615,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:18.360</t>
+          <t>2026/6/30 00:20:18.360</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -14673,7 +14673,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:23.023</t>
+          <t>2026/6/30 00:20:23.023</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -14731,7 +14731,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:27.678</t>
+          <t>2026/6/30 00:20:27.678</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -14789,7 +14789,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:32.337</t>
+          <t>2026/6/30 00:20:32.337</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -14847,7 +14847,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:37.638</t>
+          <t>2026/6/30 00:20:37.638</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -14905,7 +14905,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:42.595</t>
+          <t>2026/6/30 00:20:42.595</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -14963,7 +14963,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:47.278</t>
+          <t>2026/6/30 00:20:47.278</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -15021,7 +15021,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:51.929</t>
+          <t>2026/6/30 00:20:51.929</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -15079,7 +15079,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:57.541</t>
+          <t>2026/6/30 00:20:57.541</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -15137,7 +15137,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:02.204</t>
+          <t>2026/6/30 00:21:02.204</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -15195,7 +15195,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:06.848</t>
+          <t>2026/6/30 00:21:06.848</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -15253,7 +15253,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:11.499</t>
+          <t>2026/6/30 00:21:11.499</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:16.786</t>
+          <t>2026/6/30 00:21:16.786</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -15369,7 +15369,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:21.785</t>
+          <t>2026/6/30 00:21:21.785</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -15427,7 +15427,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:26.429</t>
+          <t>2026/6/30 00:21:26.429</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -15485,7 +15485,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:31.097</t>
+          <t>2026/6/30 00:21:31.097</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -15543,7 +15543,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:36.373</t>
+          <t>2026/6/30 00:21:36.373</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -15601,7 +15601,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:41.344</t>
+          <t>2026/6/30 00:21:41.344</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -15659,7 +15659,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:46.026</t>
+          <t>2026/6/30 00:21:46.026</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -15717,7 +15717,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:50.690</t>
+          <t>2026/6/30 00:21:50.690</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -15775,7 +15775,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:56.267</t>
+          <t>2026/6/30 00:21:56.267</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -15833,7 +15833,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:01.230</t>
+          <t>2026/6/30 00:22:01.230</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -15891,7 +15891,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:05.889</t>
+          <t>2026/6/30 00:22:05.889</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -15949,7 +15949,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:10.544</t>
+          <t>2026/6/30 00:22:10.544</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -16007,7 +16007,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:15.541</t>
+          <t>2026/6/30 00:22:15.541</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -16065,7 +16065,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:20.819</t>
+          <t>2026/6/30 00:22:20.819</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -16123,7 +16123,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:25.495</t>
+          <t>2026/6/30 00:22:25.495</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -16181,7 +16181,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:30.135</t>
+          <t>2026/6/30 00:22:30.135</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -16239,7 +16239,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:35.153</t>
+          <t>2026/6/30 00:22:35.153</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -16297,7 +16297,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:40.428</t>
+          <t>2026/6/30 00:22:40.428</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -16355,7 +16355,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:45.085</t>
+          <t>2026/6/30 00:22:45.085</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -16413,7 +16413,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:49.741</t>
+          <t>2026/6/30 00:22:49.741</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -16471,7 +16471,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:55.016</t>
+          <t>2026/6/30 00:22:55.016</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -16529,7 +16529,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:00.296</t>
+          <t>2026/6/30 00:23:00.296</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -16587,7 +16587,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:04.941</t>
+          <t>2026/6/30 00:23:04.941</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -16645,7 +16645,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:09.636</t>
+          <t>2026/6/30 00:23:09.636</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -16703,7 +16703,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:14.617</t>
+          <t>2026/6/30 00:23:14.617</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -16761,7 +16761,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:19.900</t>
+          <t>2026/6/30 00:23:19.900</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -16819,7 +16819,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:24.575</t>
+          <t>2026/6/30 00:23:24.575</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -16877,7 +16877,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:29.198</t>
+          <t>2026/6/30 00:23:29.198</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -16935,7 +16935,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:34.209</t>
+          <t>2026/6/30 00:23:34.209</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -16993,7 +16993,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:39.168</t>
+          <t>2026/6/30 00:23:39.168</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -17051,7 +17051,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:44.116</t>
+          <t>2026/6/30 00:23:44.116</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -17109,7 +17109,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:48.812</t>
+          <t>2026/6/30 00:23:48.812</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -17167,7 +17167,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:53.810</t>
+          <t>2026/6/30 00:23:53.810</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:59.404</t>
+          <t>2026/6/30 00:23:59.404</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:04.035</t>
+          <t>2026/6/30 00:24:04.035</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -17341,7 +17341,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:08.719</t>
+          <t>2026/6/30 00:24:08.719</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -17399,7 +17399,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:13.390</t>
+          <t>2026/6/30 00:24:13.390</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -17457,7 +17457,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:18.958</t>
+          <t>2026/6/30 00:24:18.958</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -17515,7 +17515,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:28.295</t>
+          <t>2026/6/30 00:24:28.295</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -17573,7 +17573,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:32.979</t>
+          <t>2026/6/30 00:24:32.979</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:37.937</t>
+          <t>2026/6/30 00:24:37.937</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:42.575</t>
+          <t>2026/6/30 00:24:42.575</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -17747,7 +17747,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:47.257</t>
+          <t>2026/6/30 00:24:47.257</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -17805,7 +17805,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:51.897</t>
+          <t>2026/6/30 00:24:51.897</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -17863,7 +17863,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:57.846</t>
+          <t>2026/6/30 00:24:57.846</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -17921,7 +17921,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:02.510</t>
+          <t>2026/6/30 00:25:02.510</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -17979,7 +17979,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:07.135</t>
+          <t>2026/6/30 00:25:07.135</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -18037,7 +18037,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:11.837</t>
+          <t>2026/6/30 00:25:11.837</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -18095,7 +18095,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:17.074</t>
+          <t>2026/6/30 00:25:17.074</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -18153,7 +18153,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:22.054</t>
+          <t>2026/6/30 00:25:22.054</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -18211,7 +18211,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:26.735</t>
+          <t>2026/6/30 00:25:26.735</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -18269,7 +18269,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:31.423</t>
+          <t>2026/6/30 00:25:31.423</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -18327,7 +18327,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:36.688</t>
+          <t>2026/6/30 00:25:36.688</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -18385,7 +18385,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:41.661</t>
+          <t>2026/6/30 00:25:41.661</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -18443,7 +18443,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:46.289</t>
+          <t>2026/6/30 00:25:46.289</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -18501,7 +18501,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:50.970</t>
+          <t>2026/6/30 00:25:50.970</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -18559,7 +18559,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:56.899</t>
+          <t>2026/6/30 00:25:56.899</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -18617,7 +18617,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:01.539</t>
+          <t>2026/6/30 00:26:01.539</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -18675,7 +18675,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:06.230</t>
+          <t>2026/6/30 00:26:06.230</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -18733,7 +18733,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:10.872</t>
+          <t>2026/6/30 00:26:10.872</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -18791,7 +18791,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:16.144</t>
+          <t>2026/6/30 00:26:16.144</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -18849,7 +18849,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:21.149</t>
+          <t>2026/6/30 00:26:21.149</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -18907,7 +18907,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:25.789</t>
+          <t>2026/6/30 00:26:25.789</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -18965,7 +18965,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:30.476</t>
+          <t>2026/6/30 00:26:30.476</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -19023,7 +19023,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:35.730</t>
+          <t>2026/6/30 00:26:35.730</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -19081,7 +19081,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:40.705</t>
+          <t>2026/6/30 00:26:40.705</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -19139,7 +19139,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:45.368</t>
+          <t>2026/6/30 00:26:45.368</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -19197,7 +19197,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:50.062</t>
+          <t>2026/6/30 00:26:50.062</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -19255,7 +19255,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:55.345</t>
+          <t>2026/6/30 00:26:55.345</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -19313,7 +19313,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:00.613</t>
+          <t>2026/6/30 00:27:00.613</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -19371,7 +19371,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:05.278</t>
+          <t>2026/6/30 00:27:05.278</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -19429,7 +19429,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:09.944</t>
+          <t>2026/6/30 00:27:09.944</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -19487,7 +19487,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:14.900</t>
+          <t>2026/6/30 00:27:14.900</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -19545,7 +19545,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:20.218</t>
+          <t>2026/6/30 00:27:20.218</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -19603,7 +19603,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:25.168</t>
+          <t>2026/6/30 00:27:25.168</t>
         </is>
       </c>
       <c r="C331" t="n">
@@ -19661,7 +19661,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:29.854</t>
+          <t>2026/6/30 00:27:29.854</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -19719,7 +19719,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:34.784</t>
+          <t>2026/6/30 00:27:34.784</t>
         </is>
       </c>
       <c r="C333" t="n">
@@ -19777,7 +19777,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:40.093</t>
+          <t>2026/6/30 00:27:40.093</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -19835,7 +19835,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:44.733</t>
+          <t>2026/6/30 00:27:44.733</t>
         </is>
       </c>
       <c r="C335" t="n">
@@ -19893,7 +19893,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:49.427</t>
+          <t>2026/6/30 00:27:49.427</t>
         </is>
       </c>
       <c r="C336" t="n">
@@ -19951,7 +19951,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:54.726</t>
+          <t>2026/6/30 00:27:54.726</t>
         </is>
       </c>
       <c r="C337" t="n">
@@ -20009,7 +20009,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:00.005</t>
+          <t>2026/6/30 00:28:00.005</t>
         </is>
       </c>
       <c r="C338" t="n">
@@ -20067,7 +20067,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:04.647</t>
+          <t>2026/6/30 00:28:04.647</t>
         </is>
       </c>
       <c r="C339" t="n">
@@ -20125,7 +20125,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:09.326</t>
+          <t>2026/6/30 00:28:09.326</t>
         </is>
       </c>
       <c r="C340" t="n">
@@ -20183,7 +20183,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:13.966</t>
+          <t>2026/6/30 00:28:13.966</t>
         </is>
       </c>
       <c r="C341" t="n">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:23.327</t>
+          <t>2026/6/30 00:28:23.327</t>
         </is>
       </c>
       <c r="C342" t="n">
@@ -20299,7 +20299,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:27.999</t>
+          <t>2026/6/30 00:28:27.999</t>
         </is>
       </c>
       <c r="C343" t="n">
@@ -20357,7 +20357,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:32.644</t>
+          <t>2026/6/30 00:28:32.644</t>
         </is>
       </c>
       <c r="C344" t="n">
@@ -20415,7 +20415,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:38.213</t>
+          <t>2026/6/30 00:28:38.213</t>
         </is>
       </c>
       <c r="C345" t="n">
@@ -20473,7 +20473,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:42.872</t>
+          <t>2026/6/30 00:28:42.872</t>
         </is>
       </c>
       <c r="C346" t="n">
@@ -20531,7 +20531,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:47.546</t>
+          <t>2026/6/30 00:28:47.546</t>
         </is>
       </c>
       <c r="C347" t="n">
@@ -20589,7 +20589,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:52.206</t>
+          <t>2026/6/30 00:28:52.206</t>
         </is>
       </c>
       <c r="C348" t="n">
@@ -20647,7 +20647,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:58.128</t>
+          <t>2026/6/30 00:28:58.128</t>
         </is>
       </c>
       <c r="C349" t="n">
@@ -20705,7 +20705,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:02.774</t>
+          <t>2026/6/30 00:29:02.774</t>
         </is>
       </c>
       <c r="C350" t="n">
@@ -20763,7 +20763,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:07.462</t>
+          <t>2026/6/30 00:29:07.462</t>
         </is>
       </c>
       <c r="C351" t="n">
@@ -20821,7 +20821,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:12.109</t>
+          <t>2026/6/30 00:29:12.109</t>
         </is>
       </c>
       <c r="C352" t="n">
@@ -20879,7 +20879,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:17.404</t>
+          <t>2026/6/30 00:29:17.404</t>
         </is>
       </c>
       <c r="C353" t="n">
@@ -20937,7 +20937,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:22.359</t>
+          <t>2026/6/30 00:29:22.359</t>
         </is>
       </c>
       <c r="C354" t="n">
@@ -20995,7 +20995,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:27.001</t>
+          <t>2026/6/30 00:29:27.001</t>
         </is>
       </c>
       <c r="C355" t="n">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:31.665</t>
+          <t>2026/6/30 00:29:31.665</t>
         </is>
       </c>
       <c r="C356" t="n">
@@ -21111,7 +21111,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:36.993</t>
+          <t>2026/6/30 00:29:36.993</t>
         </is>
       </c>
       <c r="C357" t="n">
@@ -21169,7 +21169,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:41.939</t>
+          <t>2026/6/30 00:29:41.939</t>
         </is>
       </c>
       <c r="C358" t="n">
@@ -21227,7 +21227,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:46.619</t>
+          <t>2026/6/30 00:29:46.619</t>
         </is>
       </c>
       <c r="C359" t="n">
@@ -21285,7 +21285,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:51.250</t>
+          <t>2026/6/30 00:29:51.250</t>
         </is>
       </c>
       <c r="C360" t="n">
@@ -21343,7 +21343,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:57.164</t>
+          <t>2026/6/30 00:29:57.164</t>
         </is>
       </c>
       <c r="C361" t="n">
@@ -21401,7 +21401,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:01.842</t>
+          <t>2026/6/30 00:30:01.842</t>
         </is>
       </c>
       <c r="C362" t="n">
@@ -21459,7 +21459,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:06.513</t>
+          <t>2026/6/30 00:30:06.513</t>
         </is>
       </c>
       <c r="C363" t="n">
@@ -21517,7 +21517,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:11.176</t>
+          <t>2026/6/30 00:30:11.176</t>
         </is>
       </c>
       <c r="C364" t="n">
@@ -21575,7 +21575,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:16.460</t>
+          <t>2026/6/30 00:30:16.460</t>
         </is>
       </c>
       <c r="C365" t="n">
@@ -21633,7 +21633,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:21.404</t>
+          <t>2026/6/30 00:30:21.404</t>
         </is>
       </c>
       <c r="C366" t="n">
@@ -21691,7 +21691,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:26.097</t>
+          <t>2026/6/30 00:30:26.097</t>
         </is>
       </c>
       <c r="C367" t="n">
@@ -21749,7 +21749,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:30.751</t>
+          <t>2026/6/30 00:30:30.751</t>
         </is>
       </c>
       <c r="C368" t="n">
@@ -21807,7 +21807,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:36.024</t>
+          <t>2026/6/30 00:30:36.024</t>
         </is>
       </c>
       <c r="C369" t="n">
@@ -21865,7 +21865,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:40.993</t>
+          <t>2026/6/30 00:30:40.993</t>
         </is>
       </c>
       <c r="C370" t="n">
@@ -21923,7 +21923,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:45.645</t>
+          <t>2026/6/30 00:30:45.645</t>
         </is>
       </c>
       <c r="C371" t="n">
@@ -21981,7 +21981,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:50.347</t>
+          <t>2026/6/30 00:30:50.347</t>
         </is>
       </c>
       <c r="C372" t="n">
@@ -22039,7 +22039,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:55.952</t>
+          <t>2026/6/30 00:30:55.952</t>
         </is>
       </c>
       <c r="C373" t="n">
@@ -22097,7 +22097,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:00.900</t>
+          <t>2026/6/30 00:31:00.900</t>
         </is>
       </c>
       <c r="C374" t="n">
@@ -22155,7 +22155,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:05.565</t>
+          <t>2026/6/30 00:31:05.565</t>
         </is>
       </c>
       <c r="C375" t="n">
@@ -22213,7 +22213,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:10.242</t>
+          <t>2026/6/30 00:31:10.242</t>
         </is>
       </c>
       <c r="C376" t="n">
@@ -22271,7 +22271,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:15.209</t>
+          <t>2026/6/30 00:31:15.209</t>
         </is>
       </c>
       <c r="C377" t="n">
@@ -22329,7 +22329,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:20.506</t>
+          <t>2026/6/30 00:31:20.506</t>
         </is>
       </c>
       <c r="C378" t="n">
@@ -22387,7 +22387,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:25.140</t>
+          <t>2026/6/30 00:31:25.140</t>
         </is>
       </c>
       <c r="C379" t="n">
@@ -22445,7 +22445,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:29.806</t>
+          <t>2026/6/30 00:31:29.806</t>
         </is>
       </c>
       <c r="C380" t="n">
@@ -22503,7 +22503,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:34.768</t>
+          <t>2026/6/30 00:31:34.768</t>
         </is>
       </c>
       <c r="C381" t="n">
@@ -22561,7 +22561,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:40.105</t>
+          <t>2026/6/30 00:31:40.105</t>
         </is>
       </c>
       <c r="C382" t="n">
@@ -22619,7 +22619,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:44.762</t>
+          <t>2026/6/30 00:31:44.762</t>
         </is>
       </c>
       <c r="C383" t="n">
@@ -22677,7 +22677,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:49.414</t>
+          <t>2026/6/30 00:31:49.414</t>
         </is>
       </c>
       <c r="C384" t="n">
@@ -22735,7 +22735,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:54.676</t>
+          <t>2026/6/30 00:31:54.676</t>
         </is>
       </c>
       <c r="C385" t="n">
@@ -22793,7 +22793,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:59.636</t>
+          <t>2026/6/30 00:31:59.636</t>
         </is>
       </c>
       <c r="C386" t="n">
@@ -22851,7 +22851,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:04.645</t>
+          <t>2026/6/30 00:32:04.645</t>
         </is>
       </c>
       <c r="C387" t="n">
@@ -22909,7 +22909,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:09.272</t>
+          <t>2026/6/30 00:32:09.272</t>
         </is>
       </c>
       <c r="C388" t="n">
@@ -22967,7 +22967,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:14.246</t>
+          <t>2026/6/30 00:32:14.246</t>
         </is>
       </c>
       <c r="C389" t="n">
@@ -23025,7 +23025,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:19.545</t>
+          <t>2026/6/30 00:32:19.545</t>
         </is>
       </c>
       <c r="C390" t="n">
@@ -23083,7 +23083,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:24.195</t>
+          <t>2026/6/30 00:32:24.195</t>
         </is>
       </c>
       <c r="C391" t="n">
@@ -23141,7 +23141,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:28.855</t>
+          <t>2026/6/30 00:32:28.855</t>
         </is>
       </c>
       <c r="C392" t="n">
@@ -23199,7 +23199,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:33.531</t>
+          <t>2026/6/30 00:32:33.531</t>
         </is>
       </c>
       <c r="C393" t="n">
@@ -23257,7 +23257,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:39.114</t>
+          <t>2026/6/30 00:32:39.114</t>
         </is>
       </c>
       <c r="C394" t="n">
@@ -23315,7 +23315,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:43.812</t>
+          <t>2026/6/30 00:32:43.812</t>
         </is>
       </c>
       <c r="C395" t="n">
@@ -23373,7 +23373,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:53.118</t>
+          <t>2026/6/30 00:32:53.118</t>
         </is>
       </c>
       <c r="C396" t="n">
@@ -23431,7 +23431,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:58.414</t>
+          <t>2026/6/30 00:32:58.414</t>
         </is>
       </c>
       <c r="C397" t="n">
@@ -23489,7 +23489,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:03.071</t>
+          <t>2026/6/30 00:33:03.071</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -23547,7 +23547,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:07.745</t>
+          <t>2026/6/30 00:33:07.745</t>
         </is>
       </c>
       <c r="C399" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:12.377</t>
+          <t>2026/6/30 00:33:12.377</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -23663,7 +23663,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:17.991</t>
+          <t>2026/6/30 00:33:17.991</t>
         </is>
       </c>
       <c r="C401" t="n">
@@ -23721,7 +23721,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:22.645</t>
+          <t>2026/6/30 00:33:22.645</t>
         </is>
       </c>
       <c r="C402" t="n">
@@ -23779,7 +23779,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:27.312</t>
+          <t>2026/6/30 00:33:27.312</t>
         </is>
       </c>
       <c r="C403" t="n">
@@ -23837,7 +23837,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:31.988</t>
+          <t>2026/6/30 00:33:31.988</t>
         </is>
       </c>
       <c r="C404" t="n">
@@ -23895,7 +23895,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:37.255</t>
+          <t>2026/6/30 00:33:37.255</t>
         </is>
       </c>
       <c r="C405" t="n">
@@ -23953,7 +23953,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:42.266</t>
+          <t>2026/6/30 00:33:42.266</t>
         </is>
       </c>
       <c r="C406" t="n">
@@ -24011,7 +24011,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:46.910</t>
+          <t>2026/6/30 00:33:46.910</t>
         </is>
       </c>
       <c r="C407" t="n">
@@ -24069,7 +24069,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:51.534</t>
+          <t>2026/6/30 00:33:51.534</t>
         </is>
       </c>
       <c r="C408" t="n">
@@ -24127,7 +24127,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:57.443</t>
+          <t>2026/6/30 00:33:57.443</t>
         </is>
       </c>
       <c r="C409" t="n">
@@ -24185,7 +24185,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:02.105</t>
+          <t>2026/6/30 00:34:02.105</t>
         </is>
       </c>
       <c r="C410" t="n">
@@ -24243,7 +24243,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:06.819</t>
+          <t>2026/6/30 00:34:06.819</t>
         </is>
       </c>
       <c r="C411" t="n">
@@ -24301,7 +24301,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:11.471</t>
+          <t>2026/6/30 00:34:11.471</t>
         </is>
       </c>
       <c r="C412" t="n">
@@ -24359,7 +24359,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:16.713</t>
+          <t>2026/6/30 00:34:16.713</t>
         </is>
       </c>
       <c r="C413" t="n">
@@ -24417,7 +24417,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:21.703</t>
+          <t>2026/6/30 00:34:21.703</t>
         </is>
       </c>
       <c r="C414" t="n">
@@ -24475,7 +24475,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:26.355</t>
+          <t>2026/6/30 00:34:26.355</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -24533,7 +24533,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:31.050</t>
+          <t>2026/6/30 00:34:31.050</t>
         </is>
       </c>
       <c r="C416" t="n">
@@ -24591,7 +24591,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:36.334</t>
+          <t>2026/6/30 00:34:36.334</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -24649,7 +24649,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:41.294</t>
+          <t>2026/6/30 00:34:41.294</t>
         </is>
       </c>
       <c r="C418" t="n">
@@ -24707,7 +24707,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:45.955</t>
+          <t>2026/6/30 00:34:45.955</t>
         </is>
       </c>
       <c r="C419" t="n">
@@ -24765,7 +24765,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:50.618</t>
+          <t>2026/6/30 00:34:50.618</t>
         </is>
       </c>
       <c r="C420" t="n">
@@ -24823,7 +24823,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:56.230</t>
+          <t>2026/6/30 00:34:56.230</t>
         </is>
       </c>
       <c r="C421" t="n">
@@ -24881,7 +24881,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:01.189</t>
+          <t>2026/6/30 00:35:01.189</t>
         </is>
       </c>
       <c r="C422" t="n">
@@ -24939,7 +24939,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:05.869</t>
+          <t>2026/6/30 00:35:05.869</t>
         </is>
       </c>
       <c r="C423" t="n">
@@ -24997,7 +24997,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:10.543</t>
+          <t>2026/6/30 00:35:10.543</t>
         </is>
       </c>
       <c r="C424" t="n">
@@ -25055,7 +25055,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:15.491</t>
+          <t>2026/6/30 00:35:15.491</t>
         </is>
       </c>
       <c r="C425" t="n">
@@ -25113,7 +25113,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:20.762</t>
+          <t>2026/6/30 00:35:20.762</t>
         </is>
       </c>
       <c r="C426" t="n">
@@ -25171,7 +25171,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:25.437</t>
+          <t>2026/6/30 00:35:25.437</t>
         </is>
       </c>
       <c r="C427" t="n">
@@ -25229,7 +25229,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:30.082</t>
+          <t>2026/6/30 00:35:30.082</t>
         </is>
       </c>
       <c r="C428" t="n">
@@ -25287,7 +25287,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:35.089</t>
+          <t>2026/6/30 00:35:35.089</t>
         </is>
       </c>
       <c r="C429" t="n">
@@ -25345,7 +25345,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:40.042</t>
+          <t>2026/6/30 00:35:40.042</t>
         </is>
       </c>
       <c r="C430" t="n">
@@ -25403,7 +25403,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:44.745</t>
+          <t>2026/6/30 00:35:44.745</t>
         </is>
       </c>
       <c r="C431" t="n">
@@ -25461,7 +25461,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:49.357</t>
+          <t>2026/6/30 00:35:49.357</t>
         </is>
       </c>
       <c r="C432" t="n">
@@ -25519,7 +25519,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:54.332</t>
+          <t>2026/6/30 00:35:54.332</t>
         </is>
       </c>
       <c r="C433" t="n">
@@ -25577,7 +25577,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:59.918</t>
+          <t>2026/6/30 00:35:59.918</t>
         </is>
       </c>
       <c r="C434" t="n">
@@ -25635,7 +25635,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:04.619</t>
+          <t>2026/6/30 00:36:04.619</t>
         </is>
       </c>
       <c r="C435" t="n">
@@ -25693,7 +25693,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:09.239</t>
+          <t>2026/6/30 00:36:09.239</t>
         </is>
       </c>
       <c r="C436" t="n">
@@ -25751,7 +25751,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:14.222</t>
+          <t>2026/6/30 00:36:14.222</t>
         </is>
       </c>
       <c r="C437" t="n">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:19.547</t>
+          <t>2026/6/30 00:36:19.547</t>
         </is>
       </c>
       <c r="C438" t="n">
@@ -25867,7 +25867,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:24.202</t>
+          <t>2026/6/30 00:36:24.202</t>
         </is>
       </c>
       <c r="C439" t="n">
@@ -25925,7 +25925,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:28.834</t>
+          <t>2026/6/30 00:36:28.834</t>
         </is>
       </c>
       <c r="C440" t="n">
@@ -25983,7 +25983,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:38.522</t>
+          <t>2026/6/30 00:36:38.522</t>
         </is>
       </c>
       <c r="C441" t="n">
@@ -26041,7 +26041,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:43.161</t>
+          <t>2026/6/30 00:36:43.161</t>
         </is>
       </c>
       <c r="C442" t="n">
@@ -26099,7 +26099,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:47.786</t>
+          <t>2026/6/30 00:36:47.786</t>
         </is>
       </c>
       <c r="C443" t="n">
@@ -26157,7 +26157,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:52.461</t>
+          <t>2026/6/30 00:36:52.461</t>
         </is>
       </c>
       <c r="C444" t="n">
@@ -26215,7 +26215,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:58.384</t>
+          <t>2026/6/30 00:36:58.384</t>
         </is>
       </c>
       <c r="C445" t="n">
@@ -26273,7 +26273,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:03.051</t>
+          <t>2026/6/30 00:37:03.051</t>
         </is>
       </c>
       <c r="C446" t="n">
@@ -26331,7 +26331,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:07.714</t>
+          <t>2026/6/30 00:37:07.714</t>
         </is>
       </c>
       <c r="C447" t="n">
@@ -26389,7 +26389,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:12.354</t>
+          <t>2026/6/30 00:37:12.354</t>
         </is>
       </c>
       <c r="C448" t="n">
@@ -26447,7 +26447,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:17.966</t>
+          <t>2026/6/30 00:37:17.966</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -26505,7 +26505,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:22.657</t>
+          <t>2026/6/30 00:37:22.657</t>
         </is>
       </c>
       <c r="C450" t="n">
@@ -26563,7 +26563,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:27.278</t>
+          <t>2026/6/30 00:37:27.278</t>
         </is>
       </c>
       <c r="C451" t="n">
@@ -26621,7 +26621,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:31.950</t>
+          <t>2026/6/30 00:37:31.950</t>
         </is>
       </c>
       <c r="C452" t="n">
@@ -26679,7 +26679,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:37.242</t>
+          <t>2026/6/30 00:37:37.242</t>
         </is>
       </c>
       <c r="C453" t="n">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:42.211</t>
+          <t>2026/6/30 00:37:42.211</t>
         </is>
       </c>
       <c r="C454" t="n">
@@ -26795,7 +26795,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:46.890</t>
+          <t>2026/6/30 00:37:46.890</t>
         </is>
       </c>
       <c r="C455" t="n">
@@ -26853,7 +26853,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:51.525</t>
+          <t>2026/6/30 00:37:51.525</t>
         </is>
       </c>
       <c r="C456" t="n">
@@ -26911,7 +26911,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:57.435</t>
+          <t>2026/6/30 00:37:57.435</t>
         </is>
       </c>
       <c r="C457" t="n">
@@ -26969,7 +26969,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:02.737</t>
+          <t>2026/6/30 00:38:02.737</t>
         </is>
       </c>
       <c r="C458" t="n">
@@ -27027,7 +27027,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:07.420</t>
+          <t>2026/6/30 00:38:07.420</t>
         </is>
       </c>
       <c r="C459" t="n">
@@ -27085,7 +27085,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:12.067</t>
+          <t>2026/6/30 00:38:12.067</t>
         </is>
       </c>
       <c r="C460" t="n">
@@ -27143,7 +27143,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:17.363</t>
+          <t>2026/6/30 00:38:17.363</t>
         </is>
       </c>
       <c r="C461" t="n">
@@ -27201,7 +27201,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:22.327</t>
+          <t>2026/6/30 00:38:22.327</t>
         </is>
       </c>
       <c r="C462" t="n">
@@ -27259,7 +27259,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:26.979</t>
+          <t>2026/6/30 00:38:26.979</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -27317,7 +27317,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:31.638</t>
+          <t>2026/6/30 00:38:31.638</t>
         </is>
       </c>
       <c r="C464" t="n">
@@ -27375,7 +27375,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:36.947</t>
+          <t>2026/6/30 00:38:36.947</t>
         </is>
       </c>
       <c r="C465" t="n">
@@ -27433,7 +27433,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:41.903</t>
+          <t>2026/6/30 00:38:41.903</t>
         </is>
       </c>
       <c r="C466" t="n">
@@ -27491,7 +27491,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:46.593</t>
+          <t>2026/6/30 00:38:46.593</t>
         </is>
       </c>
       <c r="C467" t="n">
@@ -27549,7 +27549,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:51.221</t>
+          <t>2026/6/30 00:38:51.221</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -27607,7 +27607,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:57.174</t>
+          <t>2026/6/30 00:38:57.174</t>
         </is>
       </c>
       <c r="C469" t="n">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:01.799</t>
+          <t>2026/6/30 00:39:01.799</t>
         </is>
       </c>
       <c r="C470" t="n">
@@ -27723,7 +27723,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:06.489</t>
+          <t>2026/6/30 00:39:06.489</t>
         </is>
       </c>
       <c r="C471" t="n">
@@ -27781,7 +27781,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:11.118</t>
+          <t>2026/6/30 00:39:11.118</t>
         </is>
       </c>
       <c r="C472" t="n">
@@ -27839,7 +27839,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:16.420</t>
+          <t>2026/6/30 00:39:16.420</t>
         </is>
       </c>
       <c r="C473" t="n">
@@ -27897,7 +27897,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:21.355</t>
+          <t>2026/6/30 00:39:21.355</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -27955,7 +27955,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:26.022</t>
+          <t>2026/6/30 00:39:26.022</t>
         </is>
       </c>
       <c r="C475" t="n">
@@ -28013,7 +28013,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:30.695</t>
+          <t>2026/6/30 00:39:30.695</t>
         </is>
       </c>
       <c r="C476" t="n">
@@ -28071,7 +28071,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:36.016</t>
+          <t>2026/6/30 00:39:36.016</t>
         </is>
       </c>
       <c r="C477" t="n">
@@ -28129,7 +28129,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:40.965</t>
+          <t>2026/6/30 00:39:40.965</t>
         </is>
       </c>
       <c r="C478" t="n">
@@ -28187,7 +28187,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:45.643</t>
+          <t>2026/6/30 00:39:45.643</t>
         </is>
       </c>
       <c r="C479" t="n">
@@ -28245,7 +28245,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:50.281</t>
+          <t>2026/6/30 00:39:50.281</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -28303,7 +28303,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:55.869</t>
+          <t>2026/6/30 00:39:55.869</t>
         </is>
       </c>
       <c r="C481" t="n">
@@ -28361,7 +28361,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:00.842</t>
+          <t>2026/6/30 00:40:00.842</t>
         </is>
       </c>
       <c r="C482" t="n">
@@ -28419,7 +28419,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:05.526</t>
+          <t>2026/6/30 00:40:05.526</t>
         </is>
       </c>
       <c r="C483" t="n">
@@ -28477,7 +28477,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:10.196</t>
+          <t>2026/6/30 00:40:10.196</t>
         </is>
       </c>
       <c r="C484" t="n">
@@ -28535,7 +28535,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:15.188</t>
+          <t>2026/6/30 00:40:15.188</t>
         </is>
       </c>
       <c r="C485" t="n">
@@ -28593,7 +28593,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:20.155</t>
+          <t>2026/6/30 00:40:20.155</t>
         </is>
       </c>
       <c r="C486" t="n">
@@ -28651,7 +28651,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:24.837</t>
+          <t>2026/6/30 00:40:24.837</t>
         </is>
       </c>
       <c r="C487" t="n">
@@ -28709,7 +28709,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:29.478</t>
+          <t>2026/6/30 00:40:29.478</t>
         </is>
       </c>
       <c r="C488" t="n">
@@ -28767,7 +28767,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:34.426</t>
+          <t>2026/6/30 00:40:34.426</t>
         </is>
       </c>
       <c r="C489" t="n">
@@ -28825,7 +28825,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:39.724</t>
+          <t>2026/6/30 00:40:39.724</t>
         </is>
       </c>
       <c r="C490" t="n">
@@ -28883,7 +28883,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:44.371</t>
+          <t>2026/6/30 00:40:44.371</t>
         </is>
       </c>
       <c r="C491" t="n">
@@ -28941,7 +28941,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:49.054</t>
+          <t>2026/6/30 00:40:49.054</t>
         </is>
       </c>
       <c r="C492" t="n">
@@ -28999,7 +28999,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:54.030</t>
+          <t>2026/6/30 00:40:54.030</t>
         </is>
       </c>
       <c r="C493" t="n">
@@ -29057,7 +29057,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:59.628</t>
+          <t>2026/6/30 00:40:59.628</t>
         </is>
       </c>
       <c r="C494" t="n">
@@ -29115,7 +29115,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:04.283</t>
+          <t>2026/6/30 00:41:04.283</t>
         </is>
       </c>
       <c r="C495" t="n">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:08.957</t>
+          <t>2026/6/30 00:41:08.957</t>
         </is>
       </c>
       <c r="C496" t="n">
@@ -29231,7 +29231,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:18.277</t>
+          <t>2026/6/30 00:41:18.277</t>
         </is>
       </c>
       <c r="C497" t="n">
@@ -29289,7 +29289,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:22.905</t>
+          <t>2026/6/30 00:41:22.905</t>
         </is>
       </c>
       <c r="C498" t="n">
@@ -29347,7 +29347,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:27.616</t>
+          <t>2026/6/30 00:41:27.616</t>
         </is>
       </c>
       <c r="C499" t="n">
@@ -29405,7 +29405,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:32.268</t>
+          <t>2026/6/30 00:41:32.268</t>
         </is>
       </c>
       <c r="C500" t="n">
@@ -29463,7 +29463,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:36.947</t>
+          <t>2026/6/30 00:41:36.947</t>
         </is>
       </c>
       <c r="C501" t="n">
@@ -29521,7 +29521,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:41.569</t>
+          <t>2026/6/30 00:41:41.569</t>
         </is>
       </c>
       <c r="C502" t="n">
@@ -29579,7 +29579,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:46.217</t>
+          <t>2026/6/30 00:41:46.217</t>
         </is>
       </c>
       <c r="C503" t="n">
@@ -29637,7 +29637,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:50.915</t>
+          <t>2026/6/30 00:41:50.915</t>
         </is>
       </c>
       <c r="C504" t="n">
@@ -29695,7 +29695,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:55.548</t>
+          <t>2026/6/30 00:41:55.548</t>
         </is>
       </c>
       <c r="C505" t="n">
@@ -29753,7 +29753,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:00.217</t>
+          <t>2026/6/30 00:42:00.217</t>
         </is>
       </c>
       <c r="C506" t="n">
@@ -29811,7 +29811,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:04.871</t>
+          <t>2026/6/30 00:42:04.871</t>
         </is>
       </c>
       <c r="C507" t="n">
@@ -29869,7 +29869,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:09.539</t>
+          <t>2026/6/30 00:42:09.539</t>
         </is>
       </c>
       <c r="C508" t="n">
@@ -29927,7 +29927,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:14.211</t>
+          <t>2026/6/30 00:42:14.211</t>
         </is>
       </c>
       <c r="C509" t="n">
@@ -29985,7 +29985,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:18.886</t>
+          <t>2026/6/30 00:42:18.886</t>
         </is>
       </c>
       <c r="C510" t="n">
@@ -30043,7 +30043,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:28.205</t>
+          <t>2026/6/30 00:42:28.205</t>
         </is>
       </c>
       <c r="C511" t="n">
@@ -30101,7 +30101,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:32.863</t>
+          <t>2026/6/30 00:42:32.863</t>
         </is>
       </c>
       <c r="C512" t="n">
@@ -30159,7 +30159,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:37.521</t>
+          <t>2026/6/30 00:42:37.521</t>
         </is>
       </c>
       <c r="C513" t="n">
@@ -30217,7 +30217,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:42.197</t>
+          <t>2026/6/30 00:42:42.197</t>
         </is>
       </c>
       <c r="C514" t="n">
@@ -30275,7 +30275,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:46.820</t>
+          <t>2026/6/30 00:42:46.820</t>
         </is>
       </c>
       <c r="C515" t="n">
@@ -30333,7 +30333,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:51.505</t>
+          <t>2026/6/30 00:42:51.505</t>
         </is>
       </c>
       <c r="C516" t="n">
@@ -30391,7 +30391,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:56.188</t>
+          <t>2026/6/30 00:42:56.188</t>
         </is>
       </c>
       <c r="C517" t="n">
@@ -30449,7 +30449,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:00.817</t>
+          <t>2026/6/30 00:43:00.817</t>
         </is>
       </c>
       <c r="C518" t="n">
@@ -30507,7 +30507,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:05.517</t>
+          <t>2026/6/30 00:43:05.517</t>
         </is>
       </c>
       <c r="C519" t="n">
@@ -30565,7 +30565,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:10.192</t>
+          <t>2026/6/30 00:43:10.192</t>
         </is>
       </c>
       <c r="C520" t="n">
@@ -30623,7 +30623,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:14.854</t>
+          <t>2026/6/30 00:43:14.854</t>
         </is>
       </c>
       <c r="C521" t="n">
@@ -30681,7 +30681,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:19.468</t>
+          <t>2026/6/30 00:43:19.468</t>
         </is>
       </c>
       <c r="C522" t="n">
@@ -30739,7 +30739,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:24.151</t>
+          <t>2026/6/30 00:43:24.151</t>
         </is>
       </c>
       <c r="C523" t="n">
@@ -30797,7 +30797,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:33.460</t>
+          <t>2026/6/30 00:43:33.460</t>
         </is>
       </c>
       <c r="C524" t="n">
@@ -30855,7 +30855,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:38.133</t>
+          <t>2026/6/30 00:43:38.133</t>
         </is>
       </c>
       <c r="C525" t="n">
@@ -30913,7 +30913,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:42.803</t>
+          <t>2026/6/30 00:43:42.803</t>
         </is>
       </c>
       <c r="C526" t="n">
@@ -30971,7 +30971,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:47.462</t>
+          <t>2026/6/30 00:43:47.462</t>
         </is>
       </c>
       <c r="C527" t="n">
@@ -31029,7 +31029,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:52.141</t>
+          <t>2026/6/30 00:43:52.141</t>
         </is>
       </c>
       <c r="C528" t="n">
@@ -31087,7 +31087,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:56.800</t>
+          <t>2026/6/30 00:43:56.800</t>
         </is>
       </c>
       <c r="C529" t="n">
@@ -31145,7 +31145,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:01.477</t>
+          <t>2026/6/30 00:44:01.477</t>
         </is>
       </c>
       <c r="C530" t="n">
@@ -31203,7 +31203,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:06.131</t>
+          <t>2026/6/30 00:44:06.131</t>
         </is>
       </c>
       <c r="C531" t="n">
@@ -31261,7 +31261,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:10.783</t>
+          <t>2026/6/30 00:44:10.783</t>
         </is>
       </c>
       <c r="C532" t="n">
@@ -31319,7 +31319,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:15.439</t>
+          <t>2026/6/30 00:44:15.439</t>
         </is>
       </c>
       <c r="C533" t="n">
@@ -31377,7 +31377,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:20.084</t>
+          <t>2026/6/30 00:44:20.084</t>
         </is>
       </c>
       <c r="C534" t="n">
@@ -31435,7 +31435,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:24.785</t>
+          <t>2026/6/30 00:44:24.785</t>
         </is>
       </c>
       <c r="C535" t="n">
@@ -31493,7 +31493,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:29.448</t>
+          <t>2026/6/30 00:44:29.448</t>
         </is>
       </c>
       <c r="C536" t="n">
@@ -31551,7 +31551,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:34.108</t>
+          <t>2026/6/30 00:44:34.108</t>
         </is>
       </c>
       <c r="C537" t="n">
@@ -31609,7 +31609,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:43.418</t>
+          <t>2026/6/30 00:44:43.418</t>
         </is>
       </c>
       <c r="C538" t="n">
@@ -31667,7 +31667,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:48.071</t>
+          <t>2026/6/30 00:44:48.071</t>
         </is>
       </c>
       <c r="C539" t="n">
@@ -31725,7 +31725,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:52.772</t>
+          <t>2026/6/30 00:44:52.772</t>
         </is>
       </c>
       <c r="C540" t="n">
@@ -31783,7 +31783,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:57.434</t>
+          <t>2026/6/30 00:44:57.434</t>
         </is>
       </c>
       <c r="C541" t="n">
@@ -31841,7 +31841,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:02.059</t>
+          <t>2026/6/30 00:45:02.059</t>
         </is>
       </c>
       <c r="C542" t="n">
@@ -31899,7 +31899,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:06.721</t>
+          <t>2026/6/30 00:45:06.721</t>
         </is>
       </c>
       <c r="C543" t="n">
@@ -31957,7 +31957,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:11.409</t>
+          <t>2026/6/30 00:45:11.409</t>
         </is>
       </c>
       <c r="C544" t="n">
@@ -32015,7 +32015,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:16.072</t>
+          <t>2026/6/30 00:45:16.072</t>
         </is>
       </c>
       <c r="C545" t="n">
@@ -32073,7 +32073,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:20.732</t>
+          <t>2026/6/30 00:45:20.732</t>
         </is>
       </c>
       <c r="C546" t="n">
@@ -32131,7 +32131,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:25.354</t>
+          <t>2026/6/30 00:45:25.354</t>
         </is>
       </c>
       <c r="C547" t="n">
@@ -32189,7 +32189,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:30.042</t>
+          <t>2026/6/30 00:45:30.042</t>
         </is>
       </c>
       <c r="C548" t="n">
@@ -32247,7 +32247,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:34.706</t>
+          <t>2026/6/30 00:45:34.706</t>
         </is>
       </c>
       <c r="C549" t="n">
@@ -32305,7 +32305,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:39.341</t>
+          <t>2026/6/30 00:45:39.341</t>
         </is>
       </c>
       <c r="C550" t="n">
@@ -32363,7 +32363,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:44.045</t>
+          <t>2026/6/30 00:45:44.045</t>
         </is>
       </c>
       <c r="C551" t="n">
@@ -32421,7 +32421,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:53.352</t>
+          <t>2026/6/30 00:45:53.352</t>
         </is>
       </c>
       <c r="C552" t="n">
@@ -32479,7 +32479,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:58.007</t>
+          <t>2026/6/30 00:45:58.007</t>
         </is>
       </c>
       <c r="C553" t="n">
@@ -32537,7 +32537,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:02.692</t>
+          <t>2026/6/30 00:46:02.692</t>
         </is>
       </c>
       <c r="C554" t="n">
@@ -32595,7 +32595,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:07.354</t>
+          <t>2026/6/30 00:46:07.354</t>
         </is>
       </c>
       <c r="C555" t="n">
@@ -32653,7 +32653,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:11.994</t>
+          <t>2026/6/30 00:46:11.994</t>
         </is>
       </c>
       <c r="C556" t="n">
@@ -32711,7 +32711,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:16.652</t>
+          <t>2026/6/30 00:46:16.652</t>
         </is>
       </c>
       <c r="C557" t="n">
@@ -32769,7 +32769,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:21.354</t>
+          <t>2026/6/30 00:46:21.354</t>
         </is>
       </c>
       <c r="C558" t="n">
@@ -32827,7 +32827,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:26.013</t>
+          <t>2026/6/30 00:46:26.013</t>
         </is>
       </c>
       <c r="C559" t="n">
@@ -32885,7 +32885,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:30.658</t>
+          <t>2026/6/30 00:46:30.658</t>
         </is>
       </c>
       <c r="C560" t="n">
@@ -32943,7 +32943,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:35.305</t>
+          <t>2026/6/30 00:46:35.305</t>
         </is>
       </c>
       <c r="C561" t="n">
@@ -33001,7 +33001,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:40.010</t>
+          <t>2026/6/30 00:46:40.010</t>
         </is>
       </c>
       <c r="C562" t="n">
@@ -33059,7 +33059,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:44.620</t>
+          <t>2026/6/30 00:46:44.620</t>
         </is>
       </c>
       <c r="C563" t="n">
@@ -33117,7 +33117,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:49.294</t>
+          <t>2026/6/30 00:46:49.294</t>
         </is>
       </c>
       <c r="C564" t="n">
@@ -33175,7 +33175,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:53.988</t>
+          <t>2026/6/30 00:46:53.988</t>
         </is>
       </c>
       <c r="C565" t="n">
@@ -33233,7 +33233,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:03.289</t>
+          <t>2026/6/30 00:47:03.289</t>
         </is>
       </c>
       <c r="C566" t="n">
@@ -33291,7 +33291,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:07.940</t>
+          <t>2026/6/30 00:47:07.940</t>
         </is>
       </c>
       <c r="C567" t="n">
@@ -33349,7 +33349,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:12.602</t>
+          <t>2026/6/30 00:47:12.602</t>
         </is>
       </c>
       <c r="C568" t="n">
@@ -33407,7 +33407,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:17.263</t>
+          <t>2026/6/30 00:47:17.263</t>
         </is>
       </c>
       <c r="C569" t="n">
@@ -33465,7 +33465,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:21.921</t>
+          <t>2026/6/30 00:47:21.921</t>
         </is>
       </c>
       <c r="C570" t="n">
@@ -33523,7 +33523,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:26.611</t>
+          <t>2026/6/30 00:47:26.611</t>
         </is>
       </c>
       <c r="C571" t="n">
@@ -33581,7 +33581,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:31.264</t>
+          <t>2026/6/30 00:47:31.264</t>
         </is>
       </c>
       <c r="C572" t="n">
@@ -33639,7 +33639,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:35.950</t>
+          <t>2026/6/30 00:47:35.950</t>
         </is>
       </c>
       <c r="C573" t="n">
@@ -33697,7 +33697,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:40.571</t>
+          <t>2026/6/30 00:47:40.571</t>
         </is>
       </c>
       <c r="C574" t="n">
@@ -33755,7 +33755,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:45.258</t>
+          <t>2026/6/30 00:47:45.258</t>
         </is>
       </c>
       <c r="C575" t="n">
@@ -33813,7 +33813,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:49.901</t>
+          <t>2026/6/30 00:47:49.901</t>
         </is>
       </c>
       <c r="C576" t="n">
@@ -33871,7 +33871,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:54.567</t>
+          <t>2026/6/30 00:47:54.567</t>
         </is>
       </c>
       <c r="C577" t="n">
